--- a/backend/data-filtering/route_table_2.xlsx
+++ b/backend/data-filtering/route_table_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\travel\backend\data-filtering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B4F888-53EF-46A0-B8F8-AC43878CE5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A2A80D-E151-42BD-A1F5-069FACBE1C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/backend/data-filtering/route_table_2.xlsx
+++ b/backend/data-filtering/route_table_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\travel\backend\data-filtering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A2A80D-E151-42BD-A1F5-069FACBE1C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983DA330-CF8B-4A98-839B-C843851A0FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -522,6 +522,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
